--- a/Excel/HorseDataq.xlsx
+++ b/Excel/HorseDataq.xlsx
@@ -194,7 +194,7 @@
     <t>时间戳 -1代表空闲状态</t>
   </si>
   <si>
-    <t>F-00WW-SU-B1-O2-DP04</t>
+    <t>F-00-YY-PU-Y1-B2-DP15</t>
   </si>
   <si>
     <t>小赤兔</t>
@@ -206,7 +206,7 @@
     <t>null</t>
   </si>
   <si>
-    <t>F-00GG-CA-Y1-G2-DP12</t>
+    <t>F-00-YY-CA-O1-G2-DP19</t>
   </si>
   <si>
     <t>小赤兔1</t>
@@ -215,7 +215,7 @@
     <t>3｜3</t>
   </si>
   <si>
-    <t>F-00WW-PU-R1-Y2-DP00</t>
+    <t>F-00-GG-SU-W1-R2-DP03</t>
   </si>
   <si>
     <t>小赤兔2</t>
@@ -224,7 +224,7 @@
     <t>3｜4</t>
   </si>
   <si>
-    <t>F-00WW-OC-Y1-O2-DP04</t>
+    <t>F-00-BB-OC-O1-R2-DP13</t>
   </si>
   <si>
     <t>小赤兔3</t>
@@ -233,7 +233,7 @@
     <t>3｜5</t>
   </si>
   <si>
-    <t>F-00GG-SU-Y1-W2-DP09</t>
+    <t>F-00-YY-GR-O1-R2-DP11</t>
   </si>
   <si>
     <t>小赤兔4</t>
@@ -242,7 +242,7 @@
     <t>3｜6</t>
   </si>
   <si>
-    <t>F-00YY-SU-R1-B2-DP17</t>
+    <t>F-00-WW-GR-W1-Y2-DP16</t>
   </si>
   <si>
     <t>小赤兔5</t>
@@ -251,7 +251,7 @@
     <t>3｜7</t>
   </si>
   <si>
-    <t>F-00BB-PU-O1-Y2-DP03</t>
+    <t>F-00-RR-CA-W1-W2-DP09</t>
   </si>
   <si>
     <t>小赤兔6</t>
@@ -260,7 +260,7 @@
     <t>3｜8</t>
   </si>
   <si>
-    <t>F-00WW-CA-Y1-R2-DP03</t>
+    <t>F-00-WW-OC-O1-G2-DP14</t>
   </si>
   <si>
     <t>小赤兔7</t>
@@ -269,7 +269,7 @@
     <t>3｜9</t>
   </si>
   <si>
-    <t>F-00GG-GR-W1-G2-DP19</t>
+    <t>F-00-YY-CA-O1-O2-DP09</t>
   </si>
   <si>
     <t>小赤兔8</t>
@@ -278,7 +278,7 @@
     <t>3｜10</t>
   </si>
   <si>
-    <t>F-00BB-GR-W1-G2-DP02</t>
+    <t>F-00-YY-OC-R1-O2-DP16</t>
   </si>
   <si>
     <t>小赤兔9</t>
@@ -287,7 +287,7 @@
     <t>3｜11</t>
   </si>
   <si>
-    <t>F-00YY-GR-G1-R2-DP15</t>
+    <t>F-00-RR-CA-B1-G2-DP10</t>
   </si>
   <si>
     <t>小赤兔11</t>
@@ -296,7 +296,7 @@
     <t>3｜12</t>
   </si>
   <si>
-    <t>F-00WW-GR-Y1-B2-DP11</t>
+    <t>F-00-BB-SU-B1-Y2-DP05</t>
   </si>
   <si>
     <t>小赤兔112</t>
@@ -305,7 +305,7 @@
     <t>3｜13</t>
   </si>
   <si>
-    <t>F-00GG-SU-B1-R2-DP06</t>
+    <t>F-00-BB-OC-G1-B2-DP18</t>
   </si>
   <si>
     <t>小赤兔123</t>
@@ -314,7 +314,7 @@
     <t>3｜14</t>
   </si>
   <si>
-    <t>F-00YY-SU-B1-W2-DP09</t>
+    <t>F-00-YY-GR-G1-Y2-DP13</t>
   </si>
   <si>
     <t>小赤兔1234</t>
@@ -323,7 +323,7 @@
     <t>3｜15</t>
   </si>
   <si>
-    <t>F-00BB-PU-B1-W2-DP06</t>
+    <t>F-00-GG-PU-O1-B2-DP19</t>
   </si>
   <si>
     <t>3｜16</t>
